--- a/data/excel/alert_rules.xlsx
+++ b/data/excel/alert_rules.xlsx
@@ -191,6 +191,18 @@
   </x:si>
   <x:si>
     <x:t>DisponibilidadAfectada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>preventive-overdue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Preventivo vencido</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PreventivoVencido</x:t>
+  </x:si>
+  <x:si>
+    <x:t>planificacion@example.local;supervisores@example.local;jefatura.mantenimiento@example.local</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -556,7 +568,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K14"/>
+  <x:dimension ref="A1:K15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.567768" style="0" customWidth="1"/>
@@ -568,7 +580,7 @@
     <x:col min="7" max="7" width="13.996339" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="11.996339" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="11.710625" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="89.282054" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="12.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1021,6 +1033,38 @@
       </x:c>
       <x:c r="J14" s="0" t="s">
         <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:11">
+      <x:c r="A15" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>62</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
